--- a/NECP Scenario/Results/Regional Results/KOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/KOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.894966987314023E-08</v>
+        <v>5.751338103936811E-08</v>
       </c>
       <c r="C3">
-        <v>2.26144371255918E-08</v>
+        <v>3.339167229029662E-08</v>
       </c>
       <c r="D3">
-        <v>0.1956980604254222</v>
+        <v>0.1956951171238352</v>
       </c>
       <c r="E3">
-        <v>0.2064278585862213</v>
+        <v>0.2040276575127393</v>
       </c>
       <c r="F3">
-        <v>0.3120496495664203</v>
+        <v>0.3425639722294385</v>
       </c>
       <c r="G3">
-        <v>0.641479034352355</v>
+        <v>0.5950493238412936</v>
       </c>
       <c r="H3">
-        <v>0.9628837970480688</v>
+        <v>0.896106136308816</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.310721939439105E-08</v>
+        <v>4.888637388526294E-08</v>
       </c>
       <c r="C4">
-        <v>1.922227155897488E-08</v>
+        <v>2.838292144855219E-08</v>
       </c>
       <c r="D4">
-        <v>0.1663433513618296</v>
+        <v>0.1663408495552263</v>
       </c>
       <c r="E4">
-        <v>0.1754636797983692</v>
+        <v>0.1734235088858528</v>
       </c>
       <c r="F4">
-        <v>0.265242202131025</v>
+        <v>0.2911793763950293</v>
       </c>
       <c r="G4">
-        <v>0.5452571791996015</v>
+        <v>0.5057919252649642</v>
       </c>
       <c r="H4">
-        <v>0.8184512274909195</v>
+        <v>0.7616902158625735</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.3814786548477863</v>
+        <v>0.3814786562406539</v>
       </c>
       <c r="C14">
-        <v>0.4333935214856103</v>
+        <v>0.4333935221013792</v>
       </c>
       <c r="D14">
-        <v>0.4777880654890037</v>
+        <v>0.4777879917485647</v>
       </c>
       <c r="E14">
-        <v>0.4637392920109135</v>
+        <v>0.4599320612264204</v>
       </c>
       <c r="F14">
-        <v>0.5502454836388613</v>
+        <v>0.5502455075811821</v>
       </c>
       <c r="G14">
-        <v>0.6774910179421654</v>
+        <v>0.6774910554648877</v>
       </c>
       <c r="H14">
-        <v>0.886312626368877</v>
+        <v>0.8863128532184409</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.9273550122400689</v>
+        <v>0.9273550350275119</v>
       </c>
       <c r="C28">
-        <v>1.071445234319997</v>
+        <v>1.071445245393269</v>
       </c>
       <c r="D28">
-        <v>0.2369478423121868</v>
+        <v>0.2369484294004825</v>
       </c>
       <c r="E28">
-        <v>4.610252351200615E-08</v>
+        <v>6.844907916770091E-08</v>
       </c>
       <c r="F28">
-        <v>4.408704487192741E-08</v>
+        <v>6.518691003757644E-08</v>
       </c>
       <c r="G28">
-        <v>0.00322959465842137</v>
+        <v>0.002709160025522133</v>
       </c>
       <c r="H28">
-        <v>0.009096570529829366</v>
+        <v>0.006775096300353382</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.3409393427224885</v>
+        <v>0.3409393510942136</v>
       </c>
       <c r="C29">
-        <v>0.3939136890816784</v>
+        <v>0.3939136931494188</v>
       </c>
       <c r="D29">
-        <v>0.08711317731084289</v>
+        <v>0.08711339314743309</v>
       </c>
       <c r="E29">
-        <v>1.693502639999756E-08</v>
+        <v>2.514379242434101E-08</v>
       </c>
       <c r="F29">
-        <v>1.618725484451556E-08</v>
+        <v>2.393444575892284E-08</v>
       </c>
       <c r="G29">
-        <v>0.001187350946167214</v>
+        <v>0.0009960146692070617</v>
       </c>
       <c r="H29">
-        <v>0.00334432721148635</v>
+        <v>0.002490843948787564</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.3102048028773804</v>
+        <v>0.3102037585780728</v>
       </c>
       <c r="E30">
-        <v>0.3419150010564049</v>
+        <v>0.3419145498188761</v>
       </c>
       <c r="F30">
-        <v>0.3419144830200581</v>
+        <v>0.3419137649052323</v>
       </c>
       <c r="G30">
-        <v>0.3419139919625978</v>
+        <v>0.3419130829508544</v>
       </c>
       <c r="H30">
-        <v>0.3419058662611311</v>
+        <v>0.3419005239456614</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.01458555874639467</v>
+        <v>0.01458555727517092</v>
       </c>
       <c r="C31">
-        <v>0.014585560479113</v>
+        <v>0.01458555983529845</v>
       </c>
       <c r="D31">
-        <v>0.01165281122839944</v>
+        <v>0.01165174809114487</v>
       </c>
       <c r="E31">
-        <v>0.01458475539279497</v>
+        <v>0.01458434261763536</v>
       </c>
       <c r="F31">
-        <v>0.01458426560330119</v>
+        <v>0.01458361862313956</v>
       </c>
       <c r="G31">
-        <v>0.01458380505784757</v>
+        <v>0.0145829988598662</v>
       </c>
       <c r="H31">
-        <v>0.01457653857832029</v>
+        <v>0.01457240278780942</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1.861900545085513E-07</v>
+        <v>2.722752786730002E-07</v>
       </c>
       <c r="E32">
-        <v>0.1103237581382187</v>
+        <v>0.1142946384532549</v>
       </c>
       <c r="F32">
-        <v>0.1477636927403789</v>
+        <v>0.1477636342866112</v>
       </c>
       <c r="G32">
-        <v>0.1513826540710541</v>
+        <v>0.1513826085508894</v>
       </c>
       <c r="H32">
-        <v>0.1534825598284783</v>
+        <v>0.1534827237175734</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.01701094849703767</v>
+        <v>0.01701094712054545</v>
       </c>
       <c r="C33">
-        <v>0.01701095010863023</v>
+        <v>0.01701094950180031</v>
       </c>
       <c r="D33">
-        <v>0.0170109254514034</v>
+        <v>0.01701091311916614</v>
       </c>
       <c r="E33">
-        <v>0.01598295074104308</v>
+        <v>0.01581930122919391</v>
       </c>
       <c r="F33">
-        <v>0.0155348248496608</v>
+        <v>0.0155348593884408</v>
       </c>
       <c r="G33">
-        <v>0.01624009417883104</v>
+        <v>0.01624010221660341</v>
       </c>
       <c r="H33">
-        <v>0.01679881625181824</v>
+        <v>0.01679842575703816</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.08388630472481703</v>
+        <v>0.08388252718131796</v>
       </c>
       <c r="E36">
-        <v>1.174348270394106</v>
+        <v>1.034114568805464</v>
       </c>
       <c r="F36">
-        <v>1.70024586796875</v>
+        <v>1.460025128220683</v>
       </c>
       <c r="G36">
-        <v>1.745416100479051</v>
+        <v>1.501068252690096</v>
       </c>
       <c r="H36">
-        <v>2.396138726872442</v>
+        <v>2.095752678218765</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.03373903792639709</v>
+        <v>0.0337390352481347</v>
       </c>
       <c r="C37">
-        <v>0.03373904108080537</v>
+        <v>0.03373903990916617</v>
       </c>
       <c r="D37">
-        <v>0.02403645528441158</v>
+        <v>0.02404160770034381</v>
       </c>
       <c r="E37">
-        <v>0.03032291651103544</v>
+        <v>0.03020759756420838</v>
       </c>
       <c r="F37">
-        <v>0.02889188877343459</v>
+        <v>0.02882788209703105</v>
       </c>
       <c r="G37">
-        <v>0.02889862365084098</v>
+        <v>0.02875230532535176</v>
       </c>
       <c r="H37">
-        <v>0.0288038087551386</v>
+        <v>0.02838714684729493</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1.157000782663476E-08</v>
+        <v>1.709598617438335E-08</v>
       </c>
       <c r="C38">
-        <v>5.071288636834831E-09</v>
+        <v>7.493572301979541E-09</v>
       </c>
       <c r="D38">
-        <v>0.07579769388317024</v>
+        <v>0.07579844144152251</v>
       </c>
       <c r="E38">
-        <v>0.1041620887584651</v>
+        <v>0.09496379717837018</v>
       </c>
       <c r="F38">
-        <v>0.1362447024109845</v>
+        <v>0.1362530186796396</v>
       </c>
       <c r="G38">
-        <v>0.08674445978889625</v>
+        <v>0.0909625604941303</v>
       </c>
       <c r="H38">
-        <v>0.1585836314329315</v>
+        <v>0.1801890563480493</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.894966987314023E-08</v>
+        <v>5.751338103936811E-08</v>
       </c>
       <c r="C40">
-        <v>2.26144371255918E-08</v>
+        <v>3.339167229029662E-08</v>
       </c>
       <c r="D40">
-        <v>0.1956980604254222</v>
+        <v>0.1956951171238352</v>
       </c>
       <c r="E40">
-        <v>0.2064278585862213</v>
+        <v>0.2040276575127393</v>
       </c>
       <c r="F40">
-        <v>0.3120496495664203</v>
+        <v>0.3425639722294385</v>
       </c>
       <c r="G40">
-        <v>0.641479034352355</v>
+        <v>0.5950493238412936</v>
       </c>
       <c r="H40">
-        <v>0.9628837970480688</v>
+        <v>0.896106136308816</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.310721939439105E-08</v>
+        <v>4.888637388526294E-08</v>
       </c>
       <c r="C41">
-        <v>1.922227155897488E-08</v>
+        <v>2.838292144855219E-08</v>
       </c>
       <c r="D41">
-        <v>0.1663433513618296</v>
+        <v>0.1663408495552263</v>
       </c>
       <c r="E41">
-        <v>0.1754636797983692</v>
+        <v>0.1734235088858528</v>
       </c>
       <c r="F41">
-        <v>0.265242202131025</v>
+        <v>0.2911793763950293</v>
       </c>
       <c r="G41">
-        <v>0.5452571791996015</v>
+        <v>0.5057919252649642</v>
       </c>
       <c r="H41">
-        <v>0.8184512274909195</v>
+        <v>0.7616902158625735</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.842450478749181E-09</v>
+        <v>-8.627007154105172E-09</v>
       </c>
       <c r="C42">
-        <v>-3.392165566616914E-09</v>
+        <v>-5.008750841744426E-09</v>
       </c>
       <c r="D42">
-        <v>-0.02935470906359261</v>
+        <v>-0.02935426756860898</v>
       </c>
       <c r="E42">
-        <v>-0.03096417878785207</v>
+        <v>-0.03060414862688643</v>
       </c>
       <c r="F42">
-        <v>-0.04680744743539533</v>
+        <v>-0.05138459583440919</v>
       </c>
       <c r="G42">
-        <v>-0.0962218551527535</v>
+        <v>-0.08925739857632942</v>
       </c>
       <c r="H42">
-        <v>-0.1444325695571493</v>
+        <v>-0.1344159204462425</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-1.057003422272448</v>
+        <v>-0.9208985054418193</v>
       </c>
       <c r="F43">
-        <v>-1.477354090747085</v>
+        <v>-1.232490814123065</v>
       </c>
       <c r="G43">
-        <v>-1.344460651611812</v>
+        <v>-1.106737852258698</v>
       </c>
       <c r="H43">
-        <v>-1.735936058456318</v>
+        <v>-1.444286803914541</v>
       </c>
     </row>
     <row r="44" spans="1:8">
